--- a/SGC-CKN/Excel/583e2f44-f264-44b8-b7c1-872eef9bfc9b_Lô_CT-02_P7-79_D800_22-05-2026.xlsx
+++ b/SGC-CKN/Excel/583e2f44-f264-44b8-b7c1-872eef9bfc9b_Lô_CT-02_P7-79_D800_22-05-2026.xlsx
@@ -189,7 +189,7 @@
 22/05/2026</t>
   </si>
   <si>
-    <t>Ghi chú Lót chân sỏi đá</t>
+    <t>Chạm sỏi cao độ -35,55</t>
   </si>
   <si>
     <t>10</t>
@@ -1206,7 +1206,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.5</v>
@@ -1215,10 +1215,10 @@
         <v>0.42</v>
       </c>
       <c r="I11" s="5">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>14.23</v>
+        <v>15.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1349,16 +1349,16 @@
         <v>-22</v>
       </c>
       <c r="G15" s="18">
-        <v>-26</v>
+        <v>-26.1</v>
       </c>
       <c r="H15" s="18">
         <v>0.25</v>
       </c>
       <c r="I15" s="18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" s="8">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1381,7 +1381,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="21">
-        <v>-26</v>
+        <v>-26.1</v>
       </c>
       <c r="G16" s="21">
         <v>-34.1</v>
@@ -1390,10 +1390,10 @@
         <v>0.17</v>
       </c>
       <c r="I16" s="21">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J16" s="8">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
@@ -1489,16 +1489,16 @@
         <v>-39</v>
       </c>
       <c r="G19" s="30">
-        <v>-44.82</v>
+        <v>-44</v>
       </c>
       <c r="H19" s="30">
         <v>4</v>
       </c>
       <c r="I19" s="30">
-        <v>5.82</v>
+        <v>5</v>
       </c>
       <c r="J19" s="33">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="K19" s="31" t="s">
         <v>55</v>
@@ -1521,7 +1521,7 @@
         <v>58</v>
       </c>
       <c r="F20" s="34">
-        <v>-44.82</v>
+        <v>-44</v>
       </c>
       <c r="G20" s="34">
         <v>-44.82</v>
@@ -1530,10 +1530,10 @@
         <v>0.42</v>
       </c>
       <c r="I20" s="34">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="J20" s="33">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1688,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.5</v>
@@ -1697,10 +1697,10 @@
         <v>0.42</v>
       </c>
       <c r="H2" s="5">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>14.23</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1807,16 +1807,16 @@
         <v>-22</v>
       </c>
       <c r="F6" s="18">
-        <v>-26</v>
+        <v>-26.1</v>
       </c>
       <c r="G6" s="18">
         <v>0.25</v>
       </c>
       <c r="H6" s="18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" s="8">
-        <v>16</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-26</v>
+        <v>-26.1</v>
       </c>
       <c r="F7" s="21">
         <v>-34.1</v>
@@ -1842,10 +1842,10 @@
         <v>0.17</v>
       </c>
       <c r="H7" s="21">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I7" s="8">
-        <v>48.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1923,16 +1923,16 @@
         <v>-39</v>
       </c>
       <c r="F10" s="30">
-        <v>-44.82</v>
+        <v>-44</v>
       </c>
       <c r="G10" s="30">
         <v>4</v>
       </c>
       <c r="H10" s="30">
-        <v>5.82</v>
+        <v>5</v>
       </c>
       <c r="I10" s="33">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1949,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-44.82</v>
+        <v>-44</v>
       </c>
       <c r="F11" s="34">
         <v>-44.82</v>
@@ -1958,10 +1958,10 @@
         <v>0.42</v>
       </c>
       <c r="H11" s="34">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="I11" s="33">
-        <v>0</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.82</v>
@@ -1987,10 +1987,10 @@
         <v>7.33</v>
       </c>
       <c r="H12" s="39">
-        <v>44.25</v>
+        <v>44.82</v>
       </c>
       <c r="I12" s="39">
-        <v>6.03</v>
+        <v>6.11</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/583e2f44-f264-44b8-b7c1-872eef9bfc9b_Lô_CT-02_P7-79_D800_22-05-2026.xlsx
+++ b/SGC-CKN/Excel/583e2f44-f264-44b8-b7c1-872eef9bfc9b_Lô_CT-02_P7-79_D800_22-05-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>13:05 22/05/2026</t>
+    <t>13:05 22/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>20:25 22/05/2026</t>
+    <t>20:25 22/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">13:05
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">13:30
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:50
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">14:45
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:10
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:25
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:35
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:48
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -176,7 +176,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:00
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -186,7 +186,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:00
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>Chạm sỏi cao độ -35,55</t>
@@ -199,7 +199,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:25
-22/05/2026</t>
+22/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -236,7 +236,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -308,6 +308,12 @@
     </font>
     <font>
       <color rgb="FF831843"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -403,7 +409,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -602,25 +608,25 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1311,7 +1317,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="15">
-        <v>-16.3</v>
+        <v>-16.8</v>
       </c>
       <c r="G14" s="15">
         <v>-22</v>
@@ -1320,10 +1326,10 @@
         <v>0.42</v>
       </c>
       <c r="I14" s="15">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J14" s="8">
-        <v>13.68</v>
+        <v>12.48</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1489,16 +1495,16 @@
         <v>-39</v>
       </c>
       <c r="G19" s="30">
-        <v>-44</v>
+        <v>-39.55</v>
       </c>
       <c r="H19" s="30">
         <v>4</v>
       </c>
       <c r="I19" s="30">
-        <v>5</v>
+        <v>0.55</v>
       </c>
       <c r="J19" s="33">
-        <v>1.25</v>
+        <v>0.14</v>
       </c>
       <c r="K19" s="31" t="s">
         <v>55</v>
@@ -1521,7 +1527,7 @@
         <v>58</v>
       </c>
       <c r="F20" s="34">
-        <v>-44</v>
+        <v>-39.55</v>
       </c>
       <c r="G20" s="34">
         <v>-44.82</v>
@@ -1530,10 +1536,10 @@
         <v>0.42</v>
       </c>
       <c r="I20" s="34">
-        <v>0.82</v>
-      </c>
-      <c r="J20" s="33">
-        <v>1.97</v>
+        <v>5.27</v>
+      </c>
+      <c r="J20" s="8">
+        <v>12.65</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1775,7 +1781,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-16.3</v>
+        <v>-16.8</v>
       </c>
       <c r="F5" s="15">
         <v>-22</v>
@@ -1784,10 +1790,10 @@
         <v>0.42</v>
       </c>
       <c r="H5" s="15">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I5" s="8">
-        <v>13.68</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1923,16 +1929,16 @@
         <v>-39</v>
       </c>
       <c r="F10" s="30">
-        <v>-44</v>
+        <v>-39.55</v>
       </c>
       <c r="G10" s="30">
         <v>4</v>
       </c>
       <c r="H10" s="30">
-        <v>5</v>
+        <v>0.55</v>
       </c>
       <c r="I10" s="33">
-        <v>1.25</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1949,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-44</v>
+        <v>-39.55</v>
       </c>
       <c r="F11" s="34">
         <v>-44.82</v>
@@ -1958,10 +1964,10 @@
         <v>0.42</v>
       </c>
       <c r="H11" s="34">
-        <v>0.82</v>
-      </c>
-      <c r="I11" s="33">
-        <v>1.97</v>
+        <v>5.27</v>
+      </c>
+      <c r="I11" s="8">
+        <v>12.65</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1987,10 +1993,10 @@
         <v>7.33</v>
       </c>
       <c r="H12" s="39">
-        <v>44.82</v>
+        <v>44.32</v>
       </c>
       <c r="I12" s="39">
-        <v>6.11</v>
+        <v>6.04</v>
       </c>
     </row>
   </sheetData>
